--- a/第二阶段测试用例.xlsx
+++ b/第二阶段测试用例.xlsx
@@ -2699,7 +2699,7 @@
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：[ODS] 本地　…/bigdata/ods；校验 14/14 通过</t>
+实测：[ODS] 本地　…/bigdata/ods；校验 20/20 通过</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -3363,13 +3363,13 @@
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。profiling/cleaning 均以 inferSchema=False 读入，转换与失败统计在 DWD 层完成。</t>
+实测：profiling/cleaning 均以 inferSchema=False 读入；cast_with_capture() 用影子列比对，4 表 27 列失败合计 0 行，逐表待核清单均已落地</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；SOP 6.2 明文要求</t>
+          <t>正常路径；SOP 6.2 明文要求（2026-09-15 补齐捕获后由人工核验升级为自动断言）</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.625" customWidth="1" min="1" max="1"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>验证 R001–R011 全部执行、全程零删除、校验 14 项全过、报告由产物程序生成</t>
+          <t>验证 R001–R011 全部执行、全程零删除、校验 20 项全过、报告由产物程序生成</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -3585,7 +3585,7 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：规则执行 12 条（R001–R011 及分表执行），逐条记录命中数</t>
+实测：规则执行 15 条（R001–R011 及分表执行），逐条记录命中数</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -3783,13 +3783,13 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>14 项全过；任一项不过以非零退出码结束</t>
+          <t>20 项全过；任一项不过以非零退出码结束</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：校验结果：14/14 通过　RESULT: PASS</t>
+实测：校验结果：20/20 通过　RESULT: PASS</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：质量报告已生成（140 行）；问题 11 条　规则执行 12 条　校验 14 项全过</t>
+实测：质量报告已生成（151 行）；问题 11 条　规则执行 15 条　校验 20 项全过</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -4074,32 +4074,66 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>P5-16</t>
+          <t>P5-17</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>校验不过必须拦住后续阶段</t>
+          <t>维表与事件表同样捕获转换失败</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>使 validation 的任一断言失败</t>
+          <t>t_pile / t_station / t_pile_log</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>以非零退出码结束，不允许带着失败的校验进入分析阶段</t>
+          <t>三表各落一份待核清单且为 0 行；参与转换的列非空数在 ODS 与 DWD 间逐列一致</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。validation.py 在 failed&gt;0 时以非零码返回，脚本内已实现；本轮 14/14 全过未触发该分支。</t>
+实测：t_pile 7 列、t_station 5 列、t_pile_log 3 列逐列一致；三份清单行数均为 0</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>回归；修复「失败捕获只覆盖 t_order」的缺口，见 03_rules.md 一致性核对 #3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>P5-16</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>校验不过必须拦住后续阶段</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>使 validation 的任一断言失败</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>以非零退出码结束，不允许带着失败的校验进入分析阶段</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：与预期一致（人工审核）。validation.py 在 failed&gt;0 时以非零码返回，脚本内已实现；本轮 20/20 全过未触发该分支。</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>人工审核项；异常路径，破坏性构造不在真实产物上做</t>
         </is>

--- a/第二阶段测试用例.xlsx
+++ b/第二阶段测试用例.xlsx
@@ -2699,7 +2699,7 @@
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：[ODS] 本地　…/bigdata/ods；校验 20/20 通过</t>
+实测：[ODS] 本地　…/bigdata/ods；校验 82/82 通过</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.625" customWidth="1" min="1" max="1"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>验证 R001–R011 全部执行、全程零删除、校验 20 项全过、报告由产物程序生成</t>
+          <t>验证 R001–R011 全部执行、全程零删除、校验 82 项全过、Schema 契约与主外键/范围/时序逐表断言、报告由产物程序生成</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -3585,7 +3585,7 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：规则执行 15 条（R001–R011 及分表执行），逐条记录命中数</t>
+实测：规则执行 17 条（R001–R011 及分表执行），逐条记录命中数</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -3783,13 +3783,13 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>20 项全过；任一项不过以非零退出码结束</t>
+          <t>82 项全过；任一项不过以非零退出码结束</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：校验结果：20/20 通过　RESULT: PASS</t>
+实测：校验结果：82/82 通过　RESULT: PASS</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：质量报告已生成（151 行）；问题 11 条　规则执行 15 条　校验 20 项全过</t>
+实测：质量报告已生成（458 行）；问题 11 条　规则执行 17 条　校验 82 项全过</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -4074,66 +4074,338 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>P5-17</t>
+          <t>P5-25</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>维表与事件表同样捕获转换失败</t>
+          <t>Excel 副本可直接打开且不乱码</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>t_pile / t_station / t_pile_log</t>
+          <t>归档包内的两个 .xlsx</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>三表各落一份待核清单且为 0 行；参与转换的列非空数在 ODS 与 DWD 间逐列一致</t>
+          <t>中文正常显示；金额电量为数值可直接求和；手机号/订单号仍为文本；空值留空</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：t_pile 7 列、t_station 5 列、t_pile_log 3 列逐列一致；三份清单行数均为 0</t>
+实测：ODS 14 表 / DWD 11 表各一册；首两张为「说明」「表清单」，其余按业务顺序；实测 amount=12289 为数值、phone/order_no 为文本、avatar 空单元格</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>回归；修复「失败捕获只覆盖 t_order」的缺口，见 03_rules.md 一致性核对 #3</t>
+          <t>回归；评审意见⑦。CSV 为无 BOM UTF-8，中文 Windows 的 Excel 按 GBK 解会乱码；不给 CSV 加 BOM 是因为 ODS 那份是 Spark 输入，BOM 会混进首列列名</t>
         </is>
       </c>
     </row>
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>P5-16</t>
+          <t>P5-20</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>校验不过必须拦住后续阶段</t>
+          <t>全表主外键完整</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>使 validation 的任一断言失败</t>
+          <t>11 张 DWD 表的主键与 12 条外键</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>以非零退出码结束，不允许带着失败的校验进入分析阶段</t>
+          <t>主键非空唯一；外键全部命中维表（可空外键的 NULL 不算违规）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。validation.py 在 failed&gt;0 时以非零码返回，脚本内已实现；本轮 20/20 全过未触发该分支。</t>
+实测：11 表主键全过；7 张有外键的表共 12 条关系全部命中</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>回归；评审意见②：原先只查订单表</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>P5-21</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>取值范围符合源库 CHECK</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>45 条范围规则</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>状态枚举、金额非负、评分 1–5、峰平谷求和等于总量等逐条满足</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：11 表 45 条规则全部满足；含 carbon_daily 峰平谷+未分配=总量的等式校验</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>边界值；约束在 SQLite 里生效，数据进 ODS 后无人守，DWD 必须自查</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>P5-22</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>时间连续性无缺口</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>dwd_order 按日、dwd_carbon_daily 按站按日</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>按业务频率建完整时间索引，缺失点数为 0</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：订单 60 天 60 点；碳排放 60 天 × 6 站 = 360 点，均无缺口</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；SOP 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>P5-23</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>关键分布前后完全一致</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>amount / kwh_x100 / price 与状态分布</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>计数、合计、极值、四分位、状态构成逐项相等</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：三个字段的统计量与四分位逐项相等；状态分布 已结算 6477 / 已取消 1815 一致</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；SOP 7.2，零删除零改值下标准定到最严</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>P5-24</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>报告结论不得写死</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>quality_report.py 六维结论与遗留问题</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>数字与条目均由产物现读，条件不成立的条目不出现</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：遗留问题 5 条全部由实测触发；待核条目现读 pending 样例；顺带修正原文案「8292 笔订单逐笔吻合」——实际参与校验的是 6477 笔已结算单</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>回归；评审意见⑤：硬编码换数据集会说假话</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>P5-18</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>DWD 符合 Schema 契约</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>dwd_schema.py 声明的列序/类型/可空</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>11 张表 132 列逐列一致；非空列无 NULL；列序不随实现漂移</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：11 表各 3 条断言全过；契约落地当场抓出 avatar/output_path 与 R001 的矛盾并订正</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>回归；评审意见①：缺数据字典与列序契约</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>P5-19</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>合理缺失的判定可追溯</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>01_profile.json 合理缺失登记</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>9 条登记含实测缺失率与理由，字段消失或已无缺失会标注「登记已过期」</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：9 条全部落盘；报告 3.1 节渲染成表</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>回归；评审意见③：理由原先只在运行时打印</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>P5-17</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>维表与事件表同样捕获转换失败</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>t_pile / t_station / t_pile_log</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>三表各落一份待核清单且为 0 行；参与转换的列非空数在 ODS 与 DWD 间逐列一致</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：t_pile 7 列、t_station 5 列、t_pile_log 3 列逐列一致；三份清单行数均为 0</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>回归；修复「失败捕获只覆盖 t_order」的缺口，见 03_rules.md 一致性核对 #3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>P5-16</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>校验不过必须拦住后续阶段</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>使 validation 的任一断言失败</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>以非零退出码结束，不允许带着失败的校验进入分析阶段</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-15）
+实测：与预期一致（人工审核）。validation.py 在 failed&gt;0 时以非零码返回，脚本内已实现；本轮 82/82 全过未触发该分支。</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>人工审核项；异常路径，破坏性构造不在真实产物上做</t>
         </is>

--- a/第二阶段测试用例.xlsx
+++ b/第二阶段测试用例.xlsx
@@ -16,7 +16,9 @@
     <sheet name="07 Flask 只读 API" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="08 Vue3 + DataV 大屏" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="09 Spark MLlib 建模与评估" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10 缺陷清单" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10 智能运营建议" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11 结项数据集归档包" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12 缺陷清单" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +536,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -971,68 +973,68 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>P1-12</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>HDFS 未启动时的报错可定位</t>
+          <t>两个 venv 不得混用</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>停掉 NameNode 后跑读 hdfs:// 的 job</t>
+          <t>用系统 python3（3.10）执行需要 PySpark 的脚本</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>报错并指向「NameNode 未运行」这一根因</t>
+          <t>报模块缺失或版本不匹配，而不是静默跑出错误结果</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：抛 Py4JJavaError：An error occurred while calling o33.csv——根因（连接被拒）被埋在堆栈里，首行看不出</t>
+实测：系统 python3 无 pyspark，直接 ModuleNotFoundError；.venv-phase2 正常</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>异常路径；报错不够直白，RUNBOOK 7.2 已写明「HDFS 不会开机自启」作为排障第一步</t>
+          <t>异常路径；RUNBOOK 7.1 已写明两个环境不可混用</t>
         </is>
       </c>
     </row>
     <row r="19" ht="64" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P1-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>两个 venv 不得混用</t>
+          <t>HDFS 未启动时的报错可定位</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>用系统 python3（3.10）执行需要 PySpark 的脚本</t>
+          <t>停掉 NameNode 后跑读 hdfs:// 的 job</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>报模块缺失或版本不匹配，而不是静默跑出错误结果</t>
+          <t>报错并指向「NameNode 未运行」这一根因</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：系统 python3 无 pyspark，直接 ModuleNotFoundError；.venv-phase2 正常</t>
+实测：抛 Py4JJavaError：An error occurred while calling o33.csv——根因（连接被拒）被埋在堆栈里，首行看不出</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>异常路径；RUNBOOK 7.1 已写明两个环境不可混用</t>
+          <t>异常路径；报错不够直白，RUNBOOK 7.2 已写明「HDFS 不会开机自启」作为排障第一步</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1059,1339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9.625" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10.625" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>东软电动汽车充电桩应用管理平台</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>程序版本</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>第二阶段 v1.0（大数据与机器学习子系统）</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>功能模块名</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>第二阶段 · 智能运营建议（T9）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>编制人</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>L5（数据可视化与机器学习 / SCML）</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>编制时间</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>功能特性</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>把 MLlib 的 1h / 6h / 24h 预测翻译成运营动作：D16 站点分流建议、D17 预警处置清单（含模型可信度）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>测试目的</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>验证建议全部由已有产物派生、阈值与两个 Qt 客户端一致、可信度有实测依据、重复执行结果一致</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>预置条件</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>① d12_load_forecast.json 与 bigdata/mllib/eval.json 已产出；② 执行 .venv-phase2/bin/python bigdata/spark/advice.py</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>用例说明</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>输入数据</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>预期结果</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>测试结果</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>缺陷编号</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>P10-01</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>只用已有产物派生，不重训模型、不直连业务库</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>advice.py 源码与运行日志</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>输入限于 d12 预测、ODS 两张维表与 eval.json；不得出现 charging.db 连接</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：数据源 d12_load_forecast.json / t_station.csv / t_pile.csv / eval.json；全文件无 sqlite 连接，charging.db 仅出现在说明该约束的注释里</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；CLAUDE.md 5.2 第 10 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>P10-02</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>拥堵度口径与 predict.py 同源</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>congestion = 1 − idle_pile / pile_total</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>沿用预测输出的字段直接换算，不另立口径</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：龙岗大运 idle_pile 2 / pile_total 4 → congestion_pct 50.0</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；另立口径会让大屏与客户端对同一站给出两种拥堵度</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>P10-03</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>分流阈值与两个 Qt 客户端一致</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>三处阈值常量比对</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>0.8，与管理端预警、用户端提示同一口径</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：advice.py BUSY = 0.8；user-client/main_window.cpp:52 CONGESTION_BUSY_THRESHOLD = 0.8；admin-client/forecast_page.cpp:29 CONGESTION_WARNING_THRESHOLD = 0.8</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；三处不一致会让同一时刻的建议互相矛盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>P10-04</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>无站点达到分流阈值时不得给空表</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>本轮预测最高拥堵 50% &lt; 80%</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>退到「引导」级（拥堵排前二且 ≥ 40%），并在建议文本里说明</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：d16 共 2 行，advice_level 全为「引导」；最高 from_congestion_pct 50.0，未触发 80% 分流档</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>边界值；空表会被误读成功能没做，硬凑「拥堵」又是假数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>P10-05</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>候选站必须确实更空闲</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>候选条件 拥堵 &lt; 50% 且预测空闲 ≥ 2 桩</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>推荐去向的拥堵度低于来源站，且有足够空闲桩</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：南山科技园 50% → 深圳湾公园 25%/空闲 3、宝安中心 25%/空闲 3</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；不设下限会把人引到同样满的站</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>P10-06</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>推荐按距离排序并给出公里数</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>站点经纬度 haversine 距离</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>近的排前面，建议文本含距离</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：南山科技园 → 4.0km / 6.7km；龙岗大运 → 22.3km / 23.3km，均为近者在前</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>正常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>P10-07</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>预警清单覆盖站点 × horizon</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>d17_alert_actions</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>6 站 × 1/6/24h 中触发预警的组合逐条出行</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：12 行：高峰 6 / 低谷 6；按 horizon 为 1h 1 行、6h 5 行、24h 6 行</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>正常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>P10-08</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>可信度来自实测增益，不是人为设定</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>eval.json 的 gain_vs_b_pct</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>两个目标都跑赢基线→高，赢一个→中，都没赢→低</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：1h「负荷 +1.0%、并发 +7.9%（2/2 优于基线）」→ 高；24h 1/2 → 中；6h 0/2 → 低</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；与 P9-07「结果如实报告」同源——跑输的 horizon 照样出建议，但标低可信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>P10-09</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>故障桩进入处置动作</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>t_pile status=2 的站点</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>有故障桩的站点给出抢修 / 远程重启动作</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：龙岗大运 fault_piles=1 → 「高峰前完成抢修 / 远程重启（该站 1 台故障桩）」共 4 行</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；[说明书] 远程重启电桩</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>P10-10</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>重复执行结果一致</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>连续执行 advice.py 两次</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>两张表 DROP + CREATE 重建，行内容完全相同</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：两次 rows 逐字段相同，仅 generated_at 不同</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；幂等</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>P10-11</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>结果同时落 JSON 与 MySQL 且 API 可取</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>MySQL 结果表 + /api/dimension/*</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>两侧行数一致，接口 code=0</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：MySQL d16 2 行 / d17 12 行，与 JSON 一致；两个接口均 code=0</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>正常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>P10-12</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>新增维度须自动计入 _summary</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>bigdata/analysis/_summary.json</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>dimension_count 由脚本更新，不靠手改</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：dimension_count = 15（含 D16/D17），comparison_count = 3</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>回归；rebase 后曾出现 _summary 与结果文件对不上（见提交 20001bb）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>P10-13</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>建议页在大屏渲染</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>大屏第 6 页</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>热力图 + 两张表格均出数</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：第 6 页「6智能运营建议」3 个面板　1 个非空 canvas</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；渲染侧断言见 08 表 P8-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9.625" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10.625" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>东软电动汽车充电桩应用管理平台</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>程序版本</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>第二阶段 v1.0（大数据与机器学习子系统）</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>功能模块名</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>第二阶段 · 结项数据集归档（L5）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>编制人</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>L5（数据可视化与机器学习 / SCML）</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>编制时间</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>功能特性</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>《数据清洗基本流程-操作SOP》第 8 节归档清单：原始只读快照、规则、脚本、执行日志、待核记录、清洗结果、质量报告</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>测试目的</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>验证一条命令即可导出可直接提交的数据集压缩包，且包内口径、链接与指纹全部自洽</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>预置条件</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>六阶段产物齐全；执行 .venv-phase2/bin/python scripts/pack-dataset-phase2.py</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>用例说明</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>输入数据</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>预期结果</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>测试结果</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>缺陷编号</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>P11-01</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>一条命令导出压缩包</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>pack-dataset-phase2.py</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>直接产出 export/第二阶段数据清洗数据集.zip，无需人工拼装</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：2.46 MB，解包后 85 个文件（含清单自身）；2026-09-16 16:44 一次跑通</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>正常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>P11-02</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>归档内容对齐 SOP 第 8 节</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>解包后目录</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>六阶段目录 00–06 + 脚本 + 打包清单齐全</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：00_原始层_ODS / 01_探查与质量评估 / 02_清洗规则 / 03_清洗结果_DWD / 04_执行日志与待核清单 / 05_清洗校验 / 06_质量报告 / 脚本 / _打包清单.json</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；按编号读下来就是完整清洗过程</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>P11-03</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>原始层随包归档且指纹可追溯</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>00_原始层_ODS/_manifest.json</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>源库指纹与打包清单一致，可回溯到具体的业务库快照</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：源库指纹 2eff8f6c1537b4eb；14 表 CSV + manifest + HDFS 落地留痕 _hdfs_deploy.json</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；CLAUDE.md 5.2 第 6 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>P11-04</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>DWD 同时给 parquet 与可读副本</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>03_清洗结果_DWD</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>parquet 为流水线真实产物，CSV 与 xlsx 为等价可读副本</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：11 表 parquet + 11 份 CSV + DWD清洗结果.xlsx；dwd_order.csv 8292 行与 DWD 一致</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；评阅人不装任何库也能核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>P11-05</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CSV 时间不得平移 8 小时</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>parquet 内按规范存 UTC</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>由 Spark 按会话时区导出，与同行的 order_hour 自洽</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：dwd_order.csv 8292 行逐行比对，reserve_time 的小时与 order_hour 不符 0 行；样例 2026-07-07 11:21:00 / order_hour=11</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>回归用例；用 pyarrow 直读会让 11:21 变成 03:21，而 order_hour 仍是 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>P11-06</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>整数列含空值不得被提升为浮点</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>取消单的时长类字段</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>空值写成空，整数不出现 48.0 这种写法</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：start_time / end_time / settle_time / charge_minutes / wait_minutes / unit_price_fen 各 1815 个空值；全表无小数写法</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>边界值；CLAUDE.md 5.2 第 7 条；走 pandas 会被提升成 float</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>P11-07</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Excel 副本随包产出</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ODS原始数据.xlsx / DWD清洗结果.xlsx</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>两册均在包内，首两张为「说明」「表清单」</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：ODS 14 表 / DWD 11 表，两册齐全</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；内容口径见 05 表 P5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>P11-08</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>只读位在包内恢复为可写</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ODS 源文件为 444</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>包内为 644，解压后可读可复制；只读性由指纹与质量报告证明，不靠权限位</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：包内 t_order.csv 为 -rw-r--r--，源目录仍为 444</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>边界值；直接带走 444 会让评阅人连解压后的目录都删不掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>P11-09</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Spark 校验碎片剔除、_SUCCESS 保留</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>parquet 目录</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>.crc 是噪音须删，_SUCCESS 标记写入完整须留</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：解包后 .crc 0 个，_SUCCESS 11 个</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>正常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>P11-10</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>包内相对链接不得断</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>六阶段分目录后同级路径全部失效</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>只改包内副本把链接指到新位置，仓库原件不动</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：包内 markdown 相对链接 7 条，断链 0；仓库原件未被修改</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；脚本内以 assert 守住「文档改了这里要跟着改」</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>P11-11</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>打包清单逐文件指纹可复算</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>_打包清单.json</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>每个文件的字节数与 sha256 均可独立复算</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：84 条逐条复算，不一致 0；清单自身不登记，故磁盘 85 − 登记 84 = 1</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；自己无法登记自己的指纹</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>P11-12</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>README 必须登记进清单</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>清单由扫描暂存目录生成</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>README 先写后扫，否则漏登</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：README.md 在清单内；脚本以 assert 守住写入顺序</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>回归用例；上一版曾漏登（2026-09-15 评审指出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>P11-13</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>压缩包完整性</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>unzip -t</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>全部条目可解压，无 CRC 错误</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：No errors detected in compressed data（108 个条目）</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>正常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>P11-14</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>重复打包内容一致</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>连续执行两次并逐文件比对指纹</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>数据文件逐字节一致；只允许含时间戳的文件不同</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：81/84 文件指纹相同；不同的 3 个为 README.md（含打包时间）与两册 xlsx——后者拆包后仅 docProps/core.xml 一个零件不同，即 Excel 内置创建时间，数据部分完全一致</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；幂等的边界说清楚，比笼统说「完全一致」可信</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>P11-15</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>包内不得含版本库占位文件</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>解包后查隐藏文件</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>归档包面向评阅，不应出现 .gitkeep 这类仓库内部文件</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>不通过（2026-09-16）
+实测：00_原始层_ODS/.gitkeep 随 ODS 目录整体复制进包（1 个）。不影响数据正确性，但该文件正是 BUG-P2-002 里让本地/HDFS 文件数对不上的那个</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>BUG-P2-009</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>缺陷用例；修复方式见缺陷清单，需重新打包一次</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1114,7 +2448,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>L5（数据可视化与机器学习 / SCML）　编制时间 2026-09-15</t>
+          <t>L5（数据可视化与机器学习 / SCML）　编制时间 2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -1379,59 +2713,59 @@
     <row r="10" ht="76" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>BUG-P2-006</t>
+          <t>BUG-P2-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>P3-10</t>
+          <t>P11-15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ODS 路径被 pathlib 折叠导致 hdfs:// 失效</t>
+          <t>结项数据集压缩包带入仓库占位文件 .gitkeep</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>bigdata/spark/spark_session.py</t>
+          <t>scripts/pack-dataset-phase2.py</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ODS_ROOT 曾包成 pathlib.Path，而 pathlib 会折叠连续斜杠：hdfs://localhost:9000/x 变成 hdfs:/localhost:9000/x。Spark 把它当本地相对路径找，报「Path does not exist」，完全看不出根因</t>
+          <t>ODS 目录整体 copytree 进包，把只为让 git 留住空目录而存在的 .gitkeep 一并带走。评阅人解包后会在原始层看到一个与数据无关的隐藏文件；同一个文件此前已在 BUG-P2-002 里造成过本地与 HDFS 的文件数对不上</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>严重（HDFS 通路不可用）</t>
+          <t>轻（不影响数据正确性，属交付物整洁度）</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>已修复并回归</t>
+          <t>待修复</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>T8 发现；ODS 根路径改为 str 并统一用 ods_file() 拼接。本轮由 P3-10 覆盖回归</t>
+          <t>拟在 copy() 增加忽略规则（.gitkeep 等仓库占位文件），改后需重新执行一次打包，并由 P11-11 的指纹复算与 P11-15 回归确认</t>
         </is>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>BUG-P2-007</t>
+          <t>BUG-P2-006</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>P3-11</t>
+          <t>P3-10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>_manifest.json 被 FileInputFormat 过滤，Spark 读不到</t>
+          <t>ODS 路径被 pathlib 折叠导致 hdfs:// 失效</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1441,12 +2775,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Hadoop 的 FileInputFormat 默认过滤 _ 与 . 开头的文件（_SUCCESS 即由此被忽略），而血缘清单恰好叫 _manifest.json。hdfs dfs -cat 读得到、Spark 读不到，现象矛盾易误判为文件缺失</t>
+          <t>ODS_ROOT 曾包成 pathlib.Path，而 pathlib 会折叠连续斜杠：hdfs://localhost:9000/x 变成 hdfs:/localhost:9000/x。Spark 把它当本地相对路径找，报「Path does not exist」，完全看不出根因</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>中（血缘读取失败）</t>
+          <t>严重（HDFS 通路不可用）</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1456,47 +2790,89 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>T8 发现；改用 Hadoop FileSystem.open 直读，绕开 InputFormat 过滤。本轮由 P3-11 覆盖回归</t>
+          <t>T8 发现；ODS 根路径改为 str 并统一用 ods_file() 拼接。本轮由 P3-10 覆盖回归</t>
         </is>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>BUG-P2-007</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>P3-11</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>_manifest.json 被 FileInputFormat 过滤，Spark 读不到</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>bigdata/spark/spark_session.py</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Hadoop 的 FileInputFormat 默认过滤 _ 与 . 开头的文件（_SUCCESS 即由此被忽略），而血缘清单恰好叫 _manifest.json。hdfs dfs -cat 读得到、Spark 读不到，现象矛盾易误判为文件缺失</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>中（血缘读取失败）</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>已修复并回归</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>T8 发现；改用 Hadoop FileSystem.open 直读，绕开 InputFormat 过滤。本轮由 P3-11 覆盖回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>BUG-P2-008</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>P2-06</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>export_ods.py 对 HDFS 不可用却不报错</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>bigdata/spark/export_ods.py</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>该脚本全程使用 Python 文件 I/O（mkdir / open / chmod），对 hdfs:// 无效。若按 ECP_ODS_ROOT 直接拼接，只会在本地建出一个名为 hdfs:/localhost:9000 的目录，且无人察觉</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>中（静默产生错误产物）</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>已修复并回归</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>T8 发现；显式拦截远端根路径并以退出码 2 退出，指向 scripts/ods-to-hdfs.sh。本轮由 P2-06 覆盖回归</t>
         </is>
@@ -1591,7 +2967,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -1998,68 +3374,68 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>P2-11</t>
+          <t>P2-10</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ODS 缺文件时报错明确</t>
+          <t>导出表名不接受外部输入</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>读一个不存在的 ODS 表</t>
+          <t>审查 export_ods.py 的 SQL 构造</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>报路径不存在，而不是返回空结果</t>
+          <t>表名来自本文件常量 TABLES，不来自参数或环境变量</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：AnalysisException [PATH_NOT_FOUND] Path does not exist: file:…/bigdata/ods/t_not_exist.csv</t>
+实测：与预期一致（人工审核）。表名为模块内常量列表，SELECT 语句无外部拼接点。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>异常路径；静默返回空会让下游统计悄悄归零</t>
+          <t>人工审核项；SQL 注入面审查</t>
         </is>
       </c>
     </row>
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>P2-10</t>
+          <t>P2-11</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>导出表名不接受外部输入</t>
+          <t>ODS 缺文件时报错明确</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>审查 export_ods.py 的 SQL 构造</t>
+          <t>读一个不存在的 ODS 表</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>表名来自本文件常量 TABLES，不来自参数或环境变量</t>
+          <t>报路径不存在，而不是返回空结果</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。表名为模块内常量列表，SELECT 语句无外部拼接点。</t>
+实测：AnalysisException [PATH_NOT_FOUND] Path does not exist: file:…/bigdata/ods/t_not_exist.csv</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；SQL 注入面审查</t>
+          <t>异常路径；静默返回空会让下游统计悄悄归零</t>
         </is>
       </c>
     </row>
@@ -2157,7 +3533,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -2871,7 +4247,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -3467,7 +4843,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -4074,340 +5450,340 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>P5-25</t>
+          <t>P5-16</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Excel 副本可直接打开且不乱码</t>
+          <t>校验不过必须拦住后续阶段</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>归档包内的两个 .xlsx</t>
+          <t>使 validation 的任一断言失败</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>中文正常显示；金额电量为数值可直接求和；手机号/订单号仍为文本；空值留空</t>
+          <t>以非零退出码结束，不允许带着失败的校验进入分析阶段</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：ODS 14 表 / DWD 11 表各一册；首两张为「说明」「表清单」，其余按业务顺序；实测 amount=12289 为数值、phone/order_no 为文本、avatar 空单元格</t>
+实测：与预期一致（人工审核）。validation.py 在 failed&gt;0 时以非零码返回，脚本内已实现；本轮 82/82 全过未触发该分支。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>回归；评审意见⑦。CSV 为无 BOM UTF-8，中文 Windows 的 Excel 按 GBK 解会乱码；不给 CSV 加 BOM 是因为 ODS 那份是 Spark 输入，BOM 会混进首列列名</t>
+          <t>人工审核项；异常路径，破坏性构造不在真实产物上做</t>
         </is>
       </c>
     </row>
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>P5-20</t>
+          <t>P5-17</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>全表主外键完整</t>
+          <t>维表与事件表同样捕获转换失败</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>11 张 DWD 表的主键与 12 条外键</t>
+          <t>t_pile / t_station / t_pile_log</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>主键非空唯一；外键全部命中维表（可空外键的 NULL 不算违规）</t>
+          <t>三表各落一份待核清单且为 0 行；参与转换的列非空数在 ODS 与 DWD 间逐列一致</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：11 表主键全过；7 张有外键的表共 12 条关系全部命中</t>
+实测：t_pile 7 列、t_station 5 列、t_pile_log 3 列逐列一致；三份清单行数均为 0</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>回归；评审意见②：原先只查订单表</t>
+          <t>回归；修复「失败捕获只覆盖 t_order」的缺口，见 03_rules.md 一致性核对 #3</t>
         </is>
       </c>
     </row>
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>P5-21</t>
+          <t>P5-18</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>取值范围符合源库 CHECK</t>
+          <t>DWD 符合 Schema 契约</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>45 条范围规则</t>
+          <t>dwd_schema.py 声明的列序/类型/可空</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>状态枚举、金额非负、评分 1–5、峰平谷求和等于总量等逐条满足</t>
+          <t>11 张表 132 列逐列一致；非空列无 NULL；列序不随实现漂移</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：11 表 45 条规则全部满足；含 carbon_daily 峰平谷+未分配=总量的等式校验</t>
+实测：11 表各 3 条断言全过；契约落地当场抓出 avatar/output_path 与 R001 的矛盾并订正</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>边界值；约束在 SQLite 里生效，数据进 ODS 后无人守，DWD 必须自查</t>
+          <t>回归；评审意见①：缺数据字典与列序契约</t>
         </is>
       </c>
     </row>
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>P5-22</t>
+          <t>P5-19</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>时间连续性无缺口</t>
+          <t>合理缺失的判定可追溯</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>dwd_order 按日、dwd_carbon_daily 按站按日</t>
+          <t>01_profile.json 合理缺失登记</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>按业务频率建完整时间索引，缺失点数为 0</t>
+          <t>9 条登记含实测缺失率与理由，字段消失或已无缺失会标注「登记已过期」</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：订单 60 天 60 点；碳排放 60 天 × 6 站 = 360 点，均无缺口</t>
+实测：9 条全部落盘；报告 3.1 节渲染成表</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>正常路径；SOP 6.8</t>
+          <t>回归；评审意见③：理由原先只在运行时打印</t>
         </is>
       </c>
     </row>
     <row r="27" ht="64" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>P5-23</t>
+          <t>P5-20</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>关键分布前后完全一致</t>
+          <t>全表主外键完整</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>amount / kwh_x100 / price 与状态分布</t>
+          <t>11 张 DWD 表的主键与 12 条外键</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>计数、合计、极值、四分位、状态构成逐项相等</t>
+          <t>主键非空唯一；外键全部命中维表（可空外键的 NULL 不算违规）</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：三个字段的统计量与四分位逐项相等；状态分布 已结算 6477 / 已取消 1815 一致</t>
+实测：11 表主键全过；7 张有外键的表共 12 条关系全部命中</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>正常路径；SOP 7.2，零删除零改值下标准定到最严</t>
+          <t>回归；评审意见②：原先只查订单表</t>
         </is>
       </c>
     </row>
     <row r="28" ht="64" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>P5-24</t>
+          <t>P5-21</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>报告结论不得写死</t>
+          <t>取值范围符合源库 CHECK</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>quality_report.py 六维结论与遗留问题</t>
+          <t>45 条范围规则</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>数字与条目均由产物现读，条件不成立的条目不出现</t>
+          <t>状态枚举、金额非负、评分 1–5、峰平谷求和等于总量等逐条满足</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：遗留问题 5 条全部由实测触发；待核条目现读 pending 样例；顺带修正原文案「8292 笔订单逐笔吻合」——实际参与校验的是 6477 笔已结算单</t>
+实测：11 表 45 条规则全部满足；含 carbon_daily 峰平谷+未分配=总量的等式校验</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>回归；评审意见⑤：硬编码换数据集会说假话</t>
+          <t>边界值；约束在 SQLite 里生效，数据进 ODS 后无人守，DWD 必须自查</t>
         </is>
       </c>
     </row>
     <row r="29" ht="64" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>P5-18</t>
+          <t>P5-22</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>DWD 符合 Schema 契约</t>
+          <t>时间连续性无缺口</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>dwd_schema.py 声明的列序/类型/可空</t>
+          <t>dwd_order 按日、dwd_carbon_daily 按站按日</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>11 张表 132 列逐列一致；非空列无 NULL；列序不随实现漂移</t>
+          <t>按业务频率建完整时间索引，缺失点数为 0</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：11 表各 3 条断言全过；契约落地当场抓出 avatar/output_path 与 R001 的矛盾并订正</t>
+实测：订单 60 天 60 点；碳排放 60 天 × 6 站 = 360 点，均无缺口</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>回归；评审意见①：缺数据字典与列序契约</t>
+          <t>正常路径；SOP 6.8</t>
         </is>
       </c>
     </row>
     <row r="30" ht="64" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>P5-19</t>
+          <t>P5-23</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>合理缺失的判定可追溯</t>
+          <t>关键分布前后完全一致</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>01_profile.json 合理缺失登记</t>
+          <t>amount / kwh_x100 / price 与状态分布</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>9 条登记含实测缺失率与理由，字段消失或已无缺失会标注「登记已过期」</t>
+          <t>计数、合计、极值、四分位、状态构成逐项相等</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：9 条全部落盘；报告 3.1 节渲染成表</t>
+实测：三个字段的统计量与四分位逐项相等；状态分布 已结算 6477 / 已取消 1815 一致</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>回归；评审意见③：理由原先只在运行时打印</t>
+          <t>正常路径；SOP 7.2，零删除零改值下标准定到最严</t>
         </is>
       </c>
     </row>
     <row r="31" ht="64" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>P5-17</t>
+          <t>P5-24</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>维表与事件表同样捕获转换失败</t>
+          <t>报告结论不得写死</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>t_pile / t_station / t_pile_log</t>
+          <t>quality_report.py 六维结论与遗留问题</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>三表各落一份待核清单且为 0 行；参与转换的列非空数在 ODS 与 DWD 间逐列一致</t>
+          <t>数字与条目均由产物现读，条件不成立的条目不出现</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：t_pile 7 列、t_station 5 列、t_pile_log 3 列逐列一致；三份清单行数均为 0</t>
+实测：遗留问题 5 条全部由实测触发；待核条目现读 pending 样例；顺带修正原文案「8292 笔订单逐笔吻合」——实际参与校验的是 6477 笔已结算单</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>回归；修复「失败捕获只覆盖 t_order」的缺口，见 03_rules.md 一致性核对 #3</t>
+          <t>回归；评审意见⑤：硬编码换数据集会说假话</t>
         </is>
       </c>
     </row>
     <row r="32" ht="64" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>P5-16</t>
+          <t>P5-25</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>校验不过必须拦住后续阶段</t>
+          <t>Excel 副本可直接打开且不乱码</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>使 validation 的任一断言失败</t>
+          <t>归档包内的两个 .xlsx</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>以非零退出码结束，不允许带着失败的校验进入分析阶段</t>
+          <t>中文正常显示；金额电量为数值可直接求和；手机号/订单号仍为文本；空值留空</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。validation.py 在 failed&gt;0 时以非零码返回，脚本内已实现；本轮 82/82 全过未触发该分支。</t>
+实测：ODS 14 表 / DWD 11 表各一册；首两张为「说明」「表清单」，其余按业务顺序；实测 amount=12289 为数值、phone/order_no 为文本、avatar 空单元格</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；异常路径，破坏性构造不在真实产物上做</t>
+          <t>回归；评审意见⑦。CSV 为无 BOM UTF-8，中文 Windows 的 Excel 按 GBK 解会乱码；不给 CSV 加 BOM 是因为 ODS 那份是 Spark 输入，BOM 会混进首列列名</t>
         </is>
       </c>
     </row>
@@ -4432,7 +5808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.625" customWidth="1" min="1" max="1"/>
@@ -4505,7 +5881,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -4622,8 +5998,8 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：dimension_count = 13（要求 ≥ 8）</t>
+          <t>通过（2026-09-16）
+实测：dimension_count = 15（要求 ≥ 8）；D16/D17 智能运营建议并入后自动计数，无需手改</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -4656,7 +6032,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：comparison_count = 3（C1 快慢充 / C2 工作日周末 / C3 站点对标）</t>
         </is>
       </c>
@@ -4928,8 +6304,8 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：/api/dimensions 返回 18 份（13 维度 + 4 对比表 + d12 预测表）</t>
+          <t>通过（2026-09-16）
+实测：MySQL 20 张结果表；/api/dimensions 返回 20 份（15 维度 + 4 对比表 + d12 预测表）</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -4970,6 +6346,40 @@
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>人工审核项；否则 Flask 查询压力不可控</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>P6-12</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>智能运营建议单独成表</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>bigdata/spark/advice.py → D16 / D17</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>预测结果须落到运营动作，用例见「10 智能运营建议」表</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：d16_dispatch_advice 2 行、d17_alert_actions 12 行，已计入 dimension_count</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；详见 10 表</t>
         </is>
       </c>
     </row>
@@ -5067,7 +6477,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -5184,8 +6594,8 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：维度 18 个，库连通 True</t>
+          <t>通过（2026-09-16）
+实测：维度 20 个，库连通 True</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -5218,8 +6628,8 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：共 18 份；analysis.py 新增 D11/D12 后 API 未改动即生效</t>
+          <t>通过（2026-09-16）
+实测：共 20 份；analysis.py 新增 D16/D17 后 API 未改动即生效</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -5252,8 +6662,8 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：实际 14 个（13 分析维度 + D12 预测）</t>
+          <t>通过（2026-09-16）
+实测：实际 16 个（15 分析维度 + D12 预测）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -5286,7 +6696,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：实际 3 组</t>
         </is>
       </c>
@@ -5320,7 +6730,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：营收 539362.79 元　订单 8292</t>
         </is>
       </c>
@@ -5354,7 +6764,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：revenue_fen 类型 int</t>
         </is>
       </c>
@@ -5388,7 +6798,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：settle_rate_pct 类型 float</t>
         </is>
       </c>
@@ -5426,7 +6836,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：2 行；78.11% 已结算 / 21.89% 已取消</t>
         </is>
       </c>
@@ -5460,7 +6870,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：['快充', '慢充']</t>
         </is>
       </c>
@@ -5494,7 +6904,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：各维度营收合计一致　53936279 分</t>
         </is>
       </c>
@@ -5528,7 +6938,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：code=1002</t>
         </is>
       </c>
@@ -5562,7 +6972,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：code=1002</t>
         </is>
       </c>
@@ -5596,8 +7006,8 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：仍有 18 份</t>
+          <t>通过（2026-09-16）
+实测：仍有 20 份</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -5630,7 +7040,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：code=1002</t>
         </is>
       </c>
@@ -5644,96 +7054,96 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>P7-17</t>
+          <t>P7-15</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>超长维度名</t>
+          <t>只监听回环地址</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>GET /api/dimension/&lt;500 个 a&gt;</t>
+          <t>netstat / 配置审查</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>返回 404 + 错误码，不崩、不落库查询</t>
+          <t>仅 127.0.0.1:5000，不暴露到局域网</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：HTTP 404　code=1002</t>
+实测：与预期一致（人工审核）。app.run 绑定 127.0.0.1；本服务无鉴权。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>边界值</t>
+          <t>人工审核项；[说明书] 2.2 通信安全</t>
         </is>
       </c>
     </row>
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>P7-18</t>
+          <t>P7-16</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>路径穿越尝试</t>
+          <t>接口不写任何业务库</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>GET /api/dimension/..%2F..%2Fetc%2Fpasswd</t>
+          <t>审查 app.py 的 SQL</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>被拒，返回错误码</t>
+          <t>只有 SELECT，无 INSERT/UPDATE/DELETE，不触发 Spark job</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：code=1002「接口不存在」</t>
+实测：与预期一致（人工审核）。全部语句为 SELECT，无写操作与作业调度入口。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>异常路径</t>
+          <t>人工审核项；CLAUDE.md 5.2 第 8 条</t>
         </is>
       </c>
     </row>
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>P7-19</t>
+          <t>P7-17</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>维度名为空</t>
+          <t>超长维度名</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>GET /api/dimension/</t>
+          <t>GET /api/dimension/&lt;500 个 a&gt;</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>返回 404，不进入查询分支</t>
+          <t>返回 404 + 错误码，不崩、不落库查询</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：HTTP 404</t>
+          <t>通过（2026-09-16）
+实测：HTTP 404　code=1002</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -5746,102 +7156,102 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>P7-20</t>
+          <t>P7-18</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>维度名夹带 SQL 语句</t>
+          <t>路径穿越尝试</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GET /api/dimension/d6_order_status; DROP TABLE x</t>
+          <t>GET /api/dimension/..%2F..%2Fetc%2Fpasswd</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>整串按维度名比对白名单后拒绝，不拆分执行</t>
+          <t>被拒，返回错误码</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：code=1002「维度 d6_order_status; DROP TABLE x 不存在」</t>
+          <t>通过（2026-09-16）
+实测：code=1002「接口不存在」</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>异常路径；表名会拼进 SQL，白名单是唯一防线</t>
+          <t>异常路径</t>
         </is>
       </c>
     </row>
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>P7-15</t>
+          <t>P7-19</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>只监听回环地址</t>
+          <t>维度名为空</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>netstat / 配置审查</t>
+          <t>GET /api/dimension/</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>仅 127.0.0.1:5000，不暴露到局域网</t>
+          <t>返回 404，不进入查询分支</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。app.run 绑定 127.0.0.1；本服务无鉴权。</t>
+          <t>通过（2026-09-16）
+实测：HTTP 404</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；[说明书] 2.2 通信安全</t>
+          <t>边界值</t>
         </is>
       </c>
     </row>
     <row r="27" ht="64" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>P7-16</t>
+          <t>P7-20</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>接口不写任何业务库</t>
+          <t>维度名夹带 SQL 语句</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>审查 app.py 的 SQL</t>
+          <t>GET /api/dimension/d6_order_status; DROP TABLE x</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>只有 SELECT，无 INSERT/UPDATE/DELETE，不触发 Spark job</t>
+          <t>整串按维度名比对白名单后拒绝，不拆分执行</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。全部语句为 SELECT，无写操作与作业调度入口。</t>
+          <t>通过（2026-09-16）
+实测：code=1002「维度 d6_order_status; DROP TABLE x 不存在」</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；CLAUDE.md 5.2 第 8 条</t>
+          <t>异常路径；表名会拼进 SQL，白名单是唯一防线</t>
         </is>
       </c>
     </row>
@@ -5866,7 +7276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.625" customWidth="1" min="1" max="1"/>
@@ -5939,7 +7349,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -5970,7 +7380,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>验证五页面板全部渲染出真实数据、DataV 组件生效、图表形态不单一</t>
+          <t>验证六页面板全部渲染出真实数据、DataV 组件生效、图表形态不单一</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -5987,7 +7397,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>① API 已启动；② cd bigdata/web &amp;&amp; npm run build &amp;&amp; npm run preview；③ 执行 python3 scripts/smoke-screen-phase2.py</t>
+          <t>① API 已启动；② cd bigdata/web &amp;&amp; npm run build &amp;&amp; npm run preview；③ 执行 .venv-phase2/bin/python scripts/smoke-screen-phase2.py [--url]。4173 被占用时 vite 会自动改用 4174，须把实际地址传给冒烟脚本，否则测的是别的服务</t>
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -6056,7 +7466,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：页面正常加载</t>
         </is>
       </c>
@@ -6085,13 +7495,13 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>五页标签齐全</t>
+          <t>六页标签齐全</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：5 页：['1运营总览','2站点与设备','3对比分析','4负荷预测','5碳排放']</t>
+          <t>通过（2026-09-16）
+实测：6 页：['1运营总览','2站点与设备','3对比分析','4负荷预测','5碳排放','6智能运营建议']</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -6124,7 +7534,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：5 个面板　3 个非空 canvas</t>
         </is>
       </c>
@@ -6158,7 +7568,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：4 个面板　4 个非空 canvas</t>
         </is>
       </c>
@@ -6192,7 +7602,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：4 个面板　4 个非空 canvas</t>
         </is>
       </c>
@@ -6226,7 +7636,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：2 个面板　1 个非空 canvas</t>
         </is>
       </c>
@@ -6260,7 +7670,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：3 个面板　1 个非空 canvas</t>
         </is>
       </c>
@@ -6284,18 +7694,18 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>统计五页面板总数</t>
+          <t>统计全部页面的面板总数</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>≥ 14（13 分析维度 + D12），每个维度至少占一块</t>
+          <t>下限式断言 ≥ 14，不写死会随开发增长的数</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：实际 18 个面板（15 图表 + 3 表格）</t>
+          <t>通过（2026-09-16）
+实测：实际 21 个面板（16 图表 + 5 表格）；本轮新增第 6 页 3 块后断言依旧成立，未再失效</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -6305,7 +7715,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>回归用例；该用例发现断言写死 17 已过期，见缺陷清单</t>
+          <t>回归用例；该用例发现断言写死 17 已过期，见缺陷清单。改成下限式后经历 D16/D17 两次扩页仍未误报，修法成立</t>
         </is>
       </c>
     </row>
@@ -6332,7 +7742,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：当前页 1 个非空 canvas；KPI 7 块画布最少 286 个着色像素</t>
         </is>
       </c>
@@ -6366,7 +7776,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：当前页 BorderBox13 × 3</t>
         </is>
       </c>
@@ -6400,7 +7810,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：DigitalFlop × 6</t>
         </is>
       </c>
@@ -6434,7 +7844,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：Capsule × 1　ActiveRing × 1</t>
         </is>
       </c>
@@ -6468,7 +7878,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
+          <t>通过（2026-09-16）
 实测：无</t>
         </is>
       </c>
@@ -6502,8 +7912,8 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：screenshot.png 411 KB</t>
+          <t>通过（2026-09-16）
+实测：screenshot.png 412 KB</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -6536,8 +7946,8 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。实际 9 类：折线面积 / 柱 / 横向条形 / 堆叠柱 / 分组柱 / 环图 / 仪表盘 / 雷达 / 散点，另加 3 张滚动表格。</t>
+          <t>通过（2026-09-16）
+实测：与预期一致（人工审核）。实际 10 类：折线面积 / 柱 / 横向条形 / 堆叠柱 / 分组柱 / 环图 / 仪表盘 / 雷达 / 散点 / 热力图，另加 5 张滚动表格（D12 预测明细、D13、D14、D16、D17）。热力图为第 6 页新增。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -6618,68 +8028,102 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>P8-19</t>
+          <t>P8-18</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>API 不可用时页面给出明确提示</t>
+          <t>生产构建可用</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>停掉 Flask 后刷新大屏</t>
+          <t>npm run build</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>显示全局错误提示，而不是一片空白或卡在加载态</t>
+          <t>构建成功并可由 preview 提供服务</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。App.vue 捕获取数异常并写入 state.error，由 .global-err 呈现；渲染冒烟的正向断言即检查该元素不存在。</t>
+          <t>通过（2026-09-16）
+实测：578 modules transformed；dist 产出；preview 200</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；异常路径</t>
+          <t>正常路径；冒烟跑的是生产构建而非 dev server</t>
         </is>
       </c>
     </row>
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>P8-18</t>
+          <t>P8-19</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>生产构建可用</t>
+          <t>API 不可用时页面给出明确提示</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>停掉 Flask 后刷新大屏</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>构建成功并可由 preview 提供服务</t>
+          <t>显示全局错误提示，而不是一片空白或卡在加载态</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：578 modules transformed；dist 产出；preview 200</t>
+实测：与预期一致（人工审核）。App.vue 捕获取数异常并写入 state.error，由 .global-err 呈现；渲染冒烟的正向断言即检查该元素不存在。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>正常路径；冒烟跑的是生产构建而非 dev server</t>
+          <t>人工审核项；异常路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>P8-20</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>第 6 页智能运营建议渲染</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>切到第 6 页</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>值守/检修热力图 + 分流建议表 + 预警处置表均渲染</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>通过（2026-09-16）
+实测：3 个面板　1 个非空 canvas（另两格为表格）</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>正常路径；数据侧用例见 10 表</t>
         </is>
       </c>
     </row>
@@ -6777,7 +8221,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-15（2026-09-16 增补与复跑）</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -7290,68 +8734,68 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>P9-14</t>
+          <t>P9-13</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>模型缺失时预测应报错而非写入空结果</t>
+          <t>不得用 pgrep 判断自建进程状态</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>删除/未生成模型目录后跑 predict.py</t>
+          <t>训练期间的状态检测方式</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>明确报错退出，不得向 MySQL 写入空或默认值</t>
+          <t>改用日志或 PID 文件——pgrep -f 的模式会匹配到检查进程自己</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。predict.py 以 PipelineModel.load 载入，路径不存在时抛异常中止，不进入写库分支。</t>
+实测：与预期一致（人工审核）。已从流程中移除 pgrep 判活；T7 曾因此误报「训练在跑」三个半小时。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；异常路径</t>
+          <t>人工审核项；同一个坑在 T8 以 pkill 形式再次出现</t>
         </is>
       </c>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>P9-13</t>
+          <t>P9-14</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>不得用 pgrep 判断自建进程状态</t>
+          <t>模型缺失时预测应报错而非写入空结果</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>训练期间的状态检测方式</t>
+          <t>删除/未生成模型目录后跑 predict.py</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>改用日志或 PID 文件——pgrep -f 的模式会匹配到检查进程自己</t>
+          <t>明确报错退出，不得向 MySQL 写入空或默认值</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>通过（2026-09-15）
-实测：与预期一致（人工审核）。已从流程中移除 pgrep 判活；T7 曾因此误报「训练在跑」三个半小时。</t>
+实测：与预期一致（人工审核）。predict.py 以 PipelineModel.load 载入，路径不存在时抛异常中止，不进入写库分支。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>人工审核项；同一个坑在 T8 以 pkill 形式再次出现</t>
+          <t>人工审核项；异常路径</t>
         </is>
       </c>
     </row>
